--- a/180000-200000.xlsx
+++ b/180000-200000.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
   <si>
     <t>CVR</t>
   </si>
@@ -70,6 +70,9 @@
     <t>43268570</t>
   </si>
   <si>
+    <t>31943329</t>
+  </si>
+  <si>
     <t>BPO Visma Løn og HR</t>
   </si>
   <si>
@@ -88,6 +91,9 @@
     <t>BPO Løn &amp; HR</t>
   </si>
   <si>
+    <t>BPO Løn</t>
+  </si>
+  <si>
     <t>Strategisk beslutning</t>
   </si>
   <si>
@@ -125,6 +131,9 @@
   </si>
   <si>
     <t>2024Q3</t>
+  </si>
+  <si>
+    <t>2024Q4</t>
   </si>
   <si>
     <t>180000-200000</t>
@@ -489,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -532,19 +541,19 @@
         <v>180204.78</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2">
         <v>44259</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -558,19 +567,19 @@
         <v>195393.13</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" s="2">
         <v>44587</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -584,19 +593,19 @@
         <v>186313</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" s="2">
         <v>44895</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -610,16 +619,16 @@
         <v>199392.4</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" s="2">
         <v>44950</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -633,16 +642,16 @@
         <v>193200.15</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="2">
         <v>45103</v>
       </c>
       <c r="H6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -656,19 +665,19 @@
         <v>190188</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" s="2">
         <v>45442</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -682,19 +691,19 @@
         <v>186200</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8" s="2">
         <v>45373</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -708,16 +717,16 @@
         <v>191400</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" s="2">
         <v>45476</v>
       </c>
       <c r="H9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -731,16 +740,39 @@
         <v>193860</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E10" s="2">
         <v>45526</v>
       </c>
       <c r="H10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I10" t="s">
-        <v>37</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11">
+        <v>2024</v>
+      </c>
+      <c r="C11">
+        <v>187944</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="2">
+        <v>45582</v>
+      </c>
+      <c r="H11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
